--- a/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>POAI</t>
   </si>
@@ -1266,8 +1266,8 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1369,8 +1369,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>3900</v>
       </c>
       <c r="E17" s="3">
         <v>4400</v>
@@ -1446,8 +1446,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-3200</v>
       </c>
       <c r="E18" s="3">
         <v>-3900</v>
@@ -1552,8 +1552,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1629,8 +1629,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-3000</v>
       </c>
       <c r="E21" s="3">
         <v>-3700</v>
@@ -1783,8 +1783,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
+      <c r="D23" s="3">
+        <v>-3200</v>
       </c>
       <c r="E23" s="3">
         <v>-3900</v>
@@ -2014,8 +2014,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-3200</v>
       </c>
       <c r="E26" s="3">
         <v>-3900</v>
@@ -2091,8 +2091,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-3200</v>
       </c>
       <c r="E27" s="3">
         <v>-3900</v>
@@ -2476,8 +2476,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2553,8 +2553,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-3200</v>
       </c>
       <c r="E33" s="3">
         <v>-3900</v>
@@ -2707,8 +2707,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-3200</v>
       </c>
       <c r="E35" s="3">
         <v>-3900</v>
@@ -3540,8 +3540,8 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>300</v>
       </c>
       <c r="E49" s="3">
         <v>300</v>
@@ -4138,25 +4138,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5711,8 +5711,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-3200</v>
       </c>
       <c r="E81" s="3">
         <v>-3900</v>

--- a/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>POAI</t>
   </si>
@@ -656,181 +656,188 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>500</v>
       </c>
       <c r="I8" s="3">
         <v>400</v>
       </c>
       <c r="J8" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K8" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L8" s="3">
         <v>300</v>
       </c>
       <c r="M8" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N8" s="3">
         <v>300</v>
       </c>
       <c r="O8" s="3">
+        <v>400</v>
+      </c>
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
+        <v>300</v>
+      </c>
+      <c r="R8" s="3">
         <v>500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>300</v>
-      </c>
-      <c r="S8" s="3">
-        <v>300</v>
-      </c>
-      <c r="T8" s="3">
-        <v>500</v>
       </c>
       <c r="U8" s="3">
         <v>300</v>
       </c>
       <c r="V8" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="W8" s="3">
         <v>300</v>
@@ -839,21 +846,27 @@
         <v>300</v>
       </c>
       <c r="Y8" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA8" s="3">
         <v>400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3">
         <v>200</v>
@@ -868,7 +881,7 @@
         <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J9" s="3">
         <v>100</v>
@@ -889,25 +902,25 @@
         <v>100</v>
       </c>
       <c r="P9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
         <v>100</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S9" s="3">
         <v>100</v>
       </c>
       <c r="T9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U9" s="3">
         <v>100</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
@@ -924,67 +937,73 @@
       <c r="AA9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>400</v>
       </c>
       <c r="L10" s="3">
         <v>200</v>
       </c>
       <c r="M10" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
       </c>
       <c r="O10" s="3">
+        <v>300</v>
+      </c>
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
+        <v>200</v>
+      </c>
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>200</v>
-      </c>
-      <c r="S10" s="3">
-        <v>200</v>
-      </c>
-      <c r="T10" s="3">
-        <v>300</v>
       </c>
       <c r="U10" s="3">
         <v>200</v>
       </c>
       <c r="V10" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W10" s="3">
         <v>200</v>
@@ -993,16 +1012,22 @@
         <v>200</v>
       </c>
       <c r="Y10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA10" s="3">
         <v>300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1055,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,65 +1217,71 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>3500</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>7200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>4100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>2800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>11600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>3000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>8900</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1255,19 +1294,25 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1275,11 +1320,11 @@
       <c r="F15" s="3">
         <v>0</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>8</v>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>8</v>
@@ -1290,11 +1335,11 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1338,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F17" s="3">
         <v>3900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>10900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>14500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4000</v>
-      </c>
-      <c r="R17" s="3">
-        <v>4000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>12100</v>
       </c>
       <c r="T17" s="3">
         <v>4000</v>
       </c>
       <c r="U17" s="3">
+        <v>12100</v>
+      </c>
+      <c r="V17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W17" s="3">
         <v>5400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3100</v>
-      </c>
-      <c r="X17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1800</v>
       </c>
       <c r="Z17" s="3">
         <v>2200</v>
       </c>
       <c r="AA17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AC17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-7900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-10500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-8500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-14200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-11800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1612,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1556,22 +1623,22 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1580,129 +1647,141 @@
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>6600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-3700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-10100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-8000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-5100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-11200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-4300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-13300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-3800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-3300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1778,85 +1857,97 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-11500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-13600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1881,15 +1972,15 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
@@ -1899,11 +1990,11 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1932,8 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-7900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-10400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-11500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-13600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-7900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-10400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-11500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-13700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2604,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2480,22 +2619,22 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -2504,129 +2643,141 @@
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-6600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1000</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-10400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-11500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-13700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-10400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-11500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-13700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,85 +3090,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F41" s="3">
         <v>11900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>14800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>22100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>25400</v>
-      </c>
-      <c r="I41" s="3">
-        <v>28200</v>
-      </c>
-      <c r="J41" s="3">
-        <v>25100</v>
       </c>
       <c r="K41" s="3">
         <v>28200</v>
       </c>
       <c r="L41" s="3">
+        <v>25100</v>
+      </c>
+      <c r="M41" s="3">
+        <v>28200</v>
+      </c>
+      <c r="N41" s="3">
         <v>41800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>44900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>27300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3071,10 +3250,16 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3082,13 +3267,13 @@
         <v>500</v>
       </c>
       <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>500</v>
+      </c>
+      <c r="G43" s="3">
         <v>400</v>
-      </c>
-      <c r="F43" s="3">
-        <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>300</v>
       </c>
       <c r="H43" s="3">
         <v>300</v>
@@ -3100,58 +3285,64 @@
         <v>300</v>
       </c>
       <c r="K43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L43" s="3">
         <v>300</v>
       </c>
       <c r="M43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N43" s="3">
         <v>300</v>
       </c>
       <c r="O43" s="3">
+        <v>200</v>
+      </c>
+      <c r="P43" s="3">
         <v>300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>500</v>
       </c>
       <c r="Q43" s="3">
         <v>300</v>
       </c>
       <c r="R43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="S43" s="3">
         <v>300</v>
       </c>
       <c r="T43" s="3">
+        <v>300</v>
+      </c>
+      <c r="U43" s="3">
+        <v>300</v>
+      </c>
+      <c r="V43" s="3">
         <v>600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3159,7 +3350,7 @@
         <v>400</v>
       </c>
       <c r="E44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F44" s="3">
         <v>400</v>
@@ -3168,34 +3359,34 @@
         <v>400</v>
       </c>
       <c r="H44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J44" s="3">
         <v>500</v>
       </c>
       <c r="K44" s="3">
+        <v>500</v>
+      </c>
+      <c r="L44" s="3">
+        <v>500</v>
+      </c>
+      <c r="M44" s="3">
         <v>400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>400</v>
-      </c>
-      <c r="M44" s="3">
-        <v>300</v>
-      </c>
-      <c r="N44" s="3">
-        <v>300</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
       </c>
       <c r="P44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R44" s="3">
         <v>200</v>
@@ -3207,13 +3398,13 @@
         <v>200</v>
       </c>
       <c r="U44" s="3">
+        <v>200</v>
+      </c>
+      <c r="V44" s="3">
+        <v>200</v>
+      </c>
+      <c r="W44" s="3">
         <v>300</v>
-      </c>
-      <c r="V44" s="3">
-        <v>300</v>
-      </c>
-      <c r="W44" s="3">
-        <v>200</v>
       </c>
       <c r="X44" s="3">
         <v>300</v>
@@ -3225,164 +3416,182 @@
         <v>300</v>
       </c>
       <c r="AA44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB44" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>500</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>300</v>
       </c>
       <c r="P45" s="3">
         <v>300</v>
       </c>
       <c r="Q45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R45" s="3">
         <v>300</v>
       </c>
       <c r="S45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U45" s="3">
         <v>200</v>
       </c>
       <c r="V45" s="3">
+        <v>100</v>
+      </c>
+      <c r="W45" s="3">
+        <v>200</v>
+      </c>
+      <c r="X45" s="3">
         <v>300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>300</v>
-      </c>
-      <c r="X45" s="3">
-        <v>400</v>
       </c>
       <c r="Y45" s="3">
         <v>300</v>
       </c>
       <c r="Z45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AA45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F46" s="3">
         <v>13500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>16000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>19800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>23400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>26900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>29800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>26200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>29500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>43000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>45600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>28200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1500</v>
-      </c>
-      <c r="X46" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>2000</v>
       </c>
       <c r="Z46" s="3">
         <v>3100</v>
       </c>
       <c r="AA46" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AC46" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3444,104 +3653,116 @@
         <v>0</v>
       </c>
       <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>2700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F48" s="3">
         <v>4300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>500</v>
-      </c>
-      <c r="W48" s="3">
-        <v>200</v>
-      </c>
-      <c r="X48" s="3">
-        <v>200</v>
       </c>
       <c r="Y48" s="3">
         <v>200</v>
       </c>
       <c r="Z48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB48" s="3">
         <v>100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3">
         <v>300</v>
@@ -3553,67 +3774,73 @@
         <v>300</v>
       </c>
       <c r="H49" s="3">
+        <v>300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>300</v>
+      </c>
+      <c r="J49" s="3">
         <v>3700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>10800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>10800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>6100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>6100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>6200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>16200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>19200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>19300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>19300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>28300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>28400</v>
-      </c>
-      <c r="V49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>1000</v>
       </c>
       <c r="X49" s="3">
         <v>1000</v>
       </c>
       <c r="Y49" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Z49" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA49" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3999,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3775,16 +4014,16 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -3793,25 +4032,25 @@
         <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>100</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
+      <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>100</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
@@ -3825,11 +4064,11 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -3843,8 +4082,14 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F54" s="3">
         <v>18200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>21000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>25100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>25700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>33200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>40100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>43800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>51200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>56900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>39700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>25200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>27500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>25000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>22400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>31900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>32300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>4000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>6000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,97 +4314,105 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1100</v>
       </c>
       <c r="K57" s="3">
         <v>1000</v>
       </c>
       <c r="L57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M57" s="3">
         <v>1000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>900</v>
       </c>
       <c r="N57" s="3">
         <v>1000</v>
       </c>
       <c r="O57" s="3">
+        <v>900</v>
+      </c>
+      <c r="P57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3500</v>
-      </c>
-      <c r="V57" s="3">
-        <v>400</v>
-      </c>
-      <c r="W57" s="3">
-        <v>400</v>
       </c>
       <c r="X57" s="3">
         <v>400</v>
       </c>
       <c r="Y57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>200</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4158,11 +4425,11 @@
       <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4171,46 +4438,52 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>4400</v>
       </c>
       <c r="R58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="S58" s="3">
+        <v>4400</v>
+      </c>
+      <c r="T58" s="3">
         <v>3800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>4800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>4500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4218,153 +4491,165 @@
         <v>2700</v>
       </c>
       <c r="E59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>7800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F60" s="3">
         <v>4200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2700</v>
-      </c>
-      <c r="K60" s="3">
-        <v>3200</v>
-      </c>
-      <c r="L60" s="3">
-        <v>3000</v>
       </c>
       <c r="M60" s="3">
         <v>3200</v>
       </c>
       <c r="N60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O60" s="3">
+        <v>3200</v>
+      </c>
+      <c r="P60" s="3">
         <v>3300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>9300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>14700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>12400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>10900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>10800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>9500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4411,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>2100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4440,85 +4725,97 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
       </c>
       <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>300</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,8 +5057,14 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4757,76 +5072,82 @@
         <v>6500</v>
       </c>
       <c r="E66" s="3">
-        <v>6300</v>
+        <v>6100</v>
       </c>
       <c r="F66" s="3">
         <v>6500</v>
       </c>
       <c r="G66" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>15800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>14700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>11100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>11200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>10000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-167800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-164300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-161100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-157200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-153800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-145900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-141800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-131400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-128000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-120300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-114800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-112300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-108400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-96900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-90600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-87000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-82500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-68900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-64900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-66400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-63100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-61400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-58900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-56500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-54800</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F76" s="3">
         <v>11700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>14700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>18600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>21800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>29600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>33500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>37200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>40300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>47800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>53100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>35500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>12200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>11700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>10300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>11200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>20700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>22300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>3400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>5200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-10400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-11500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-13700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5827,10 +6224,10 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
@@ -5839,13 +6236,13 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
       </c>
       <c r="M83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
@@ -5857,10 +6254,10 @@
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -5872,25 +6269,31 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-3000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-2000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6389,19 +6830,19 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -6416,49 +6857,55 @@
         <v>-200</v>
       </c>
       <c r="N91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
+      <c r="P91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-200</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,8 +7064,14 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6620,50 +7079,50 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-200</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
       </c>
       <c r="K94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-9800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -6671,25 +7130,31 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,20 +7510,26 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -7046,64 +7537,70 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>6700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>20000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>30300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>2400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>5900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>3600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>3000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>3100</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-13600</v>
       </c>
       <c r="L102" s="3">
         <v>-3100</v>
       </c>
       <c r="M102" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="O102" s="3">
         <v>17600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>26600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1000</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>POAI</t>
   </si>
@@ -656,191 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
-      </c>
-      <c r="P8" s="3">
-        <v>300</v>
       </c>
       <c r="Q8" s="3">
         <v>300</v>
       </c>
       <c r="R8" s="3">
+        <v>300</v>
+      </c>
+      <c r="S8" s="3">
         <v>500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>200</v>
-      </c>
-      <c r="T8" s="3">
-        <v>300</v>
       </c>
       <c r="U8" s="3">
         <v>300</v>
       </c>
       <c r="V8" s="3">
+        <v>300</v>
+      </c>
+      <c r="W8" s="3">
         <v>500</v>
-      </c>
-      <c r="W8" s="3">
-        <v>300</v>
       </c>
       <c r="X8" s="3">
         <v>300</v>
@@ -852,16 +856,19 @@
         <v>300</v>
       </c>
       <c r="AA8" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AB8" s="3">
         <v>400</v>
       </c>
       <c r="AC8" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -872,19 +879,19 @@
         <v>200</v>
       </c>
       <c r="F9" s="3">
+        <v>200</v>
+      </c>
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
@@ -908,10 +915,10 @@
         <v>100</v>
       </c>
       <c r="R9" s="3">
+        <v>100</v>
+      </c>
+      <c r="S9" s="3">
         <v>200</v>
-      </c>
-      <c r="S9" s="3">
-        <v>100</v>
       </c>
       <c r="T9" s="3">
         <v>100</v>
@@ -920,10 +927,10 @@
         <v>100</v>
       </c>
       <c r="V9" s="3">
+        <v>100</v>
+      </c>
+      <c r="W9" s="3">
         <v>200</v>
-      </c>
-      <c r="W9" s="3">
-        <v>100</v>
       </c>
       <c r="X9" s="3">
         <v>100</v>
@@ -943,70 +950,73 @@
       <c r="AC9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>300</v>
-      </c>
-      <c r="P10" s="3">
-        <v>200</v>
       </c>
       <c r="Q10" s="3">
         <v>200</v>
       </c>
       <c r="R10" s="3">
+        <v>200</v>
+      </c>
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>100</v>
-      </c>
-      <c r="T10" s="3">
-        <v>200</v>
       </c>
       <c r="U10" s="3">
         <v>200</v>
       </c>
       <c r="V10" s="3">
+        <v>200</v>
+      </c>
+      <c r="W10" s="3">
         <v>300</v>
-      </c>
-      <c r="W10" s="3">
-        <v>200</v>
       </c>
       <c r="X10" s="3">
         <v>200</v>
@@ -1018,16 +1028,19 @@
         <v>200</v>
       </c>
       <c r="AA10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB10" s="3">
         <v>300</v>
       </c>
       <c r="AC10" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD10" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,68 +1240,71 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>3500</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>7200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>4100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>11600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8900</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1300,14 +1320,17 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1315,7 +1338,7 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1326,8 +1349,8 @@
       <c r="H15" s="3">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>8</v>
+      <c r="I15" s="3">
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>8</v>
@@ -1341,8 +1364,8 @@
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E17" s="3">
         <v>4700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6100</v>
-      </c>
-      <c r="S17" s="3">
-        <v>4000</v>
       </c>
       <c r="T17" s="3">
         <v>4000</v>
       </c>
       <c r="U17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V17" s="3">
         <v>12100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1623,25 +1657,25 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
@@ -1653,135 +1687,141 @@
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-600</v>
       </c>
       <c r="Z20" s="3">
         <v>-600</v>
       </c>
       <c r="AA20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-11200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-13300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-2400</v>
       </c>
       <c r="AA21" s="3">
         <v>-2400</v>
       </c>
       <c r="AB21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1863,91 +1903,97 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1978,12 +2024,12 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
@@ -1996,8 +2042,8 @@
       <c r="R24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-11500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-11500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-13700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2619,25 +2689,25 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
@@ -2649,135 +2719,141 @@
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>600</v>
       </c>
       <c r="Z32" s="3">
         <v>600</v>
       </c>
       <c r="AA32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-13700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-13700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3178,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
         <v>5200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>200</v>
-      </c>
-      <c r="V41" s="3">
-        <v>100</v>
       </c>
       <c r="W41" s="3">
         <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>200</v>
       </c>
       <c r="Z41" s="3">
         <v>200</v>
       </c>
       <c r="AA41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB41" s="3">
         <v>1000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3256,27 +3346,30 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
-      </c>
-      <c r="H43" s="3">
-        <v>300</v>
       </c>
       <c r="I43" s="3">
         <v>300</v>
@@ -3291,25 +3384,25 @@
         <v>300</v>
       </c>
       <c r="M43" s="3">
+        <v>300</v>
+      </c>
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>300</v>
       </c>
       <c r="Q43" s="3">
         <v>300</v>
       </c>
       <c r="R43" s="3">
+        <v>300</v>
+      </c>
+      <c r="S43" s="3">
         <v>500</v>
-      </c>
-      <c r="S43" s="3">
-        <v>300</v>
       </c>
       <c r="T43" s="3">
         <v>300</v>
@@ -3318,42 +3411,45 @@
         <v>300</v>
       </c>
       <c r="V43" s="3">
+        <v>300</v>
+      </c>
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>600</v>
+      </c>
+      <c r="E44" s="3">
         <v>400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>500</v>
-      </c>
-      <c r="F44" s="3">
-        <v>400</v>
       </c>
       <c r="G44" s="3">
         <v>400</v>
@@ -3365,7 +3461,7 @@
         <v>400</v>
       </c>
       <c r="J44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K44" s="3">
         <v>500</v>
@@ -3374,13 +3470,13 @@
         <v>500</v>
       </c>
       <c r="M44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N44" s="3">
         <v>400</v>
       </c>
       <c r="O44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P44" s="3">
         <v>300</v>
@@ -3389,7 +3485,7 @@
         <v>300</v>
       </c>
       <c r="R44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S44" s="3">
         <v>200</v>
@@ -3404,69 +3500,72 @@
         <v>200</v>
       </c>
       <c r="W44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X44" s="3">
         <v>300</v>
       </c>
       <c r="Y44" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z44" s="3">
         <v>200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>200</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>300</v>
       </c>
       <c r="AC44" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>500</v>
       </c>
       <c r="I45" s="3">
         <v>500</v>
       </c>
       <c r="J45" s="3">
+        <v>500</v>
+      </c>
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
-      </c>
-      <c r="P45" s="3">
-        <v>300</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
@@ -3475,123 +3574,129 @@
         <v>300</v>
       </c>
       <c r="S45" s="3">
+        <v>300</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
-      </c>
-      <c r="X45" s="3">
-        <v>300</v>
       </c>
       <c r="Y45" s="3">
         <v>300</v>
       </c>
       <c r="Z45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E46" s="3">
         <v>6600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>26200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>43000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>28200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>800</v>
-      </c>
-      <c r="V46" s="3">
-        <v>1100</v>
       </c>
       <c r="W46" s="3">
         <v>1100</v>
       </c>
       <c r="X46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y46" s="3">
         <v>3700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3659,90 +3764,93 @@
         <v>0</v>
       </c>
       <c r="Y47" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="3">
         <v>1100</v>
       </c>
       <c r="AA47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB47" s="3">
         <v>1700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5100</v>
-      </c>
-      <c r="P48" s="3">
-        <v>5200</v>
       </c>
       <c r="Q48" s="3">
         <v>5200</v>
       </c>
       <c r="R48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="S48" s="3">
         <v>5500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>500</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>200</v>
       </c>
       <c r="Z48" s="3">
         <v>200</v>
@@ -3751,13 +3859,16 @@
         <v>200</v>
       </c>
       <c r="AB48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC48" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3765,7 +3876,7 @@
         <v>200</v>
       </c>
       <c r="E49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F49" s="3">
         <v>300</v>
@@ -3780,49 +3891,49 @@
         <v>300</v>
       </c>
       <c r="J49" s="3">
+        <v>300</v>
+      </c>
+      <c r="K49" s="3">
         <v>3700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3800</v>
-      </c>
-      <c r="L49" s="3">
-        <v>10800</v>
       </c>
       <c r="M49" s="3">
         <v>10800</v>
       </c>
       <c r="N49" s="3">
+        <v>10800</v>
+      </c>
+      <c r="O49" s="3">
         <v>3200</v>
-      </c>
-      <c r="O49" s="3">
-        <v>6100</v>
       </c>
       <c r="P49" s="3">
         <v>6100</v>
       </c>
       <c r="Q49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="R49" s="3">
         <v>6200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19200</v>
-      </c>
-      <c r="T49" s="3">
-        <v>19300</v>
       </c>
       <c r="U49" s="3">
         <v>19300</v>
       </c>
       <c r="V49" s="3">
+        <v>19300</v>
+      </c>
+      <c r="W49" s="3">
         <v>28300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>28400</v>
-      </c>
-      <c r="X49" s="3">
-        <v>1000</v>
       </c>
       <c r="Y49" s="3">
         <v>1000</v>
@@ -3831,7 +3942,7 @@
         <v>1000</v>
       </c>
       <c r="AA49" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB49" s="3">
         <v>100</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4122,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4020,13 +4140,13 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -4038,13 +4158,13 @@
         <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -4052,8 +4172,8 @@
       <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
+      <c r="R52" s="3">
+        <v>100</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
@@ -4070,8 +4190,8 @@
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,8 +4294,11 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4180,82 +4306,85 @@
         <v>10600</v>
       </c>
       <c r="E54" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F54" s="3">
         <v>14400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>43800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>51200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>56900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>39700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,73 +4446,74 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>900</v>
       </c>
       <c r="J57" s="3">
         <v>900</v>
       </c>
       <c r="K57" s="3">
+        <v>900</v>
+      </c>
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1000</v>
       </c>
       <c r="N57" s="3">
         <v>1000</v>
       </c>
       <c r="O57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3500</v>
-      </c>
-      <c r="X57" s="3">
-        <v>400</v>
       </c>
       <c r="Y57" s="3">
         <v>400</v>
@@ -4391,31 +4522,34 @@
         <v>400</v>
       </c>
       <c r="AA57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AB57" s="3">
         <v>200</v>
       </c>
       <c r="AC57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4431,8 +4565,8 @@
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4444,212 +4578,221 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>4400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2700</v>
       </c>
       <c r="G59" s="3">
         <v>2700</v>
       </c>
       <c r="H59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E60" s="3">
         <v>4500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>3900</v>
       </c>
       <c r="I60" s="3">
         <v>3900</v>
       </c>
       <c r="J60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K60" s="3">
         <v>3500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4702,11 +4845,11 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>2100</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4731,28 +4874,31 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
@@ -4761,47 +4907,47 @@
         <v>100</v>
       </c>
       <c r="L62" s="3">
+        <v>100</v>
+      </c>
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>300</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4811,11 +4957,14 @@
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,8 +5218,11 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5072,82 +5230,85 @@
         <v>6500</v>
       </c>
       <c r="E66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F66" s="3">
         <v>6100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-175200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-172000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-167800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-164300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-161100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-157200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-153800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-145900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-141800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-131400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-128000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-120300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-114800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-112300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-108400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-96900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-90600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-87000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-82500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-68900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-64900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-66400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-63100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-61400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-56500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-54800</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,8 +6024,11 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5850,82 +6036,85 @@
         <v>4100</v>
       </c>
       <c r="E76" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F76" s="3">
         <v>8300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>33500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>40300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>47800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>35500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>22300</v>
-      </c>
-      <c r="X76" s="3">
-        <v>100</v>
       </c>
       <c r="Y76" s="3">
         <v>100</v>
       </c>
       <c r="Z76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA76" s="3">
         <v>3000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-13700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6230,7 +6429,7 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
@@ -6242,10 +6441,10 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
@@ -6260,7 +6459,7 @@
         <v>300</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
@@ -6275,25 +6474,28 @@
         <v>200</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
       <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-3100</v>
       </c>
       <c r="F89" s="3">
         <v>-3100</v>
       </c>
       <c r="G89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-2000</v>
       </c>
       <c r="X89" s="3">
         <v>-2000</v>
       </c>
       <c r="Y89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6836,52 +7057,52 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
+      <c r="U91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
@@ -6889,23 +7110,26 @@
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7085,47 +7315,47 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
       </c>
       <c r="K94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9800</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-200</v>
       </c>
       <c r="O94" s="3">
         <v>-200</v>
       </c>
       <c r="P94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-400</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -7136,25 +7366,28 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
       </c>
       <c r="AA94" s="3">
         <v>-100</v>
       </c>
       <c r="AB94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC94" s="3">
         <v>100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,23 +7759,26 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-100</v>
+        <v>3400</v>
       </c>
       <c r="E100" s="3">
         <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -7543,64 +7789,67 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>6700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>20000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>30300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2200</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>300</v>
       </c>
       <c r="AA100" s="3">
         <v>300</v>
       </c>
       <c r="AB100" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC100" s="3">
         <v>3000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1000</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>POAI</t>
   </si>
@@ -656,133 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -790,64 +794,64 @@
         <v>300</v>
       </c>
       <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>400</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>300</v>
       </c>
       <c r="R8" s="3">
         <v>300</v>
       </c>
       <c r="S8" s="3">
+        <v>300</v>
+      </c>
+      <c r="T8" s="3">
         <v>500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>300</v>
       </c>
       <c r="V8" s="3">
         <v>300</v>
       </c>
       <c r="W8" s="3">
+        <v>300</v>
+      </c>
+      <c r="X8" s="3">
         <v>500</v>
-      </c>
-      <c r="X8" s="3">
-        <v>300</v>
       </c>
       <c r="Y8" s="3">
         <v>300</v>
@@ -859,16 +863,19 @@
         <v>300</v>
       </c>
       <c r="AB8" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AC8" s="3">
         <v>400</v>
       </c>
       <c r="AD8" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -882,19 +889,19 @@
         <v>200</v>
       </c>
       <c r="G9" s="3">
+        <v>200</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>100</v>
       </c>
       <c r="L9" s="3">
         <v>100</v>
@@ -918,10 +925,10 @@
         <v>100</v>
       </c>
       <c r="S9" s="3">
+        <v>100</v>
+      </c>
+      <c r="T9" s="3">
         <v>200</v>
-      </c>
-      <c r="T9" s="3">
-        <v>100</v>
       </c>
       <c r="U9" s="3">
         <v>100</v>
@@ -930,10 +937,10 @@
         <v>100</v>
       </c>
       <c r="W9" s="3">
+        <v>100</v>
+      </c>
+      <c r="X9" s="3">
         <v>200</v>
-      </c>
-      <c r="X9" s="3">
-        <v>100</v>
       </c>
       <c r="Y9" s="3">
         <v>100</v>
@@ -953,8 +960,11 @@
       <c r="AD9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,64 +972,64 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>300</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>200</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
       </c>
       <c r="S10" s="3">
+        <v>200</v>
+      </c>
+      <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>100</v>
-      </c>
-      <c r="U10" s="3">
-        <v>200</v>
       </c>
       <c r="V10" s="3">
         <v>200</v>
       </c>
       <c r="W10" s="3">
+        <v>200</v>
+      </c>
+      <c r="X10" s="3">
         <v>300</v>
-      </c>
-      <c r="X10" s="3">
-        <v>200</v>
       </c>
       <c r="Y10" s="3">
         <v>200</v>
@@ -1031,16 +1041,19 @@
         <v>200</v>
       </c>
       <c r="AB10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC10" s="3">
         <v>300</v>
       </c>
       <c r="AD10" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE10" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1084,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1099,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1157,8 +1171,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,71 +1260,74 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>3500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>7200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>4100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>11600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8900</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1323,37 +1343,40 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
+        <v>200</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
@@ -1367,8 +1390,8 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3800</v>
       </c>
-      <c r="G17" s="3">
-        <v>3900</v>
-      </c>
       <c r="H17" s="3">
-        <v>4400</v>
+        <v>3400</v>
       </c>
       <c r="I17" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J17" s="3">
         <v>3700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6100</v>
-      </c>
-      <c r="T17" s="3">
-        <v>4000</v>
       </c>
       <c r="U17" s="3">
         <v>4000</v>
       </c>
       <c r="V17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W17" s="3">
         <v>12100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3200</v>
       </c>
-      <c r="E18" s="3">
-        <v>-4300</v>
-      </c>
       <c r="F18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H18" s="3">
-        <v>-3900</v>
+        <v>-2700</v>
       </c>
       <c r="I18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-3500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,8 +1681,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,16 +1694,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1678,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
@@ -1690,161 +1724,167 @@
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-600</v>
       </c>
       <c r="AA20" s="3">
         <v>-600</v>
       </c>
       <c r="AB20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="X21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-3300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-11200</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="AA21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="X21" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-2400</v>
       </c>
       <c r="AB21" s="3">
         <v>-2400</v>
       </c>
       <c r="AC21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1906,94 +1946,100 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2027,12 +2073,12 @@
       <c r="M24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>-700</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
@@ -2045,8 +2091,8 @@
       <c r="S24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2078,8 +2124,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,13 +2480,16 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2440,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2747,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2692,16 +2762,16 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2710,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
@@ -2722,138 +2792,144 @@
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>600</v>
       </c>
       <c r="AA32" s="3">
         <v>600</v>
       </c>
       <c r="AB32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1000</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,94 +3265,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E41" s="3">
         <v>5300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>27300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>200</v>
-      </c>
-      <c r="W41" s="3">
-        <v>100</v>
       </c>
       <c r="X41" s="3">
         <v>100</v>
       </c>
       <c r="Y41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z41" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>200</v>
       </c>
       <c r="AA41" s="3">
         <v>200</v>
       </c>
       <c r="AB41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC41" s="3">
         <v>1000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3349,30 +3439,33 @@
         <v>0</v>
       </c>
       <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
-      </c>
-      <c r="I43" s="3">
-        <v>300</v>
       </c>
       <c r="J43" s="3">
         <v>300</v>
@@ -3387,25 +3480,25 @@
         <v>300</v>
       </c>
       <c r="N43" s="3">
+        <v>300</v>
+      </c>
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>300</v>
       </c>
       <c r="R43" s="3">
         <v>300</v>
       </c>
       <c r="S43" s="3">
+        <v>300</v>
+      </c>
+      <c r="T43" s="3">
         <v>500</v>
-      </c>
-      <c r="T43" s="3">
-        <v>300</v>
       </c>
       <c r="U43" s="3">
         <v>300</v>
@@ -3414,45 +3507,48 @@
         <v>300</v>
       </c>
       <c r="W43" s="3">
+        <v>300</v>
+      </c>
+      <c r="X43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>500</v>
+      </c>
+      <c r="E44" s="3">
         <v>600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>400</v>
       </c>
       <c r="H44" s="3">
         <v>400</v>
@@ -3464,7 +3560,7 @@
         <v>400</v>
       </c>
       <c r="K44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L44" s="3">
         <v>500</v>
@@ -3473,13 +3569,13 @@
         <v>500</v>
       </c>
       <c r="N44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O44" s="3">
         <v>400</v>
       </c>
       <c r="P44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q44" s="3">
         <v>300</v>
@@ -3488,7 +3584,7 @@
         <v>300</v>
       </c>
       <c r="S44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T44" s="3">
         <v>200</v>
@@ -3503,72 +3599,75 @@
         <v>200</v>
       </c>
       <c r="X44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y44" s="3">
         <v>300</v>
       </c>
       <c r="Z44" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA44" s="3">
         <v>200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>200</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>300</v>
       </c>
       <c r="AD44" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>500</v>
+      </c>
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="M45" s="3">
+        <v>800</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
-        <v>400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>600</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>300</v>
       </c>
       <c r="R45" s="3">
         <v>300</v>
@@ -3577,149 +3676,155 @@
         <v>300</v>
       </c>
       <c r="T45" s="3">
+        <v>300</v>
+      </c>
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>300</v>
       </c>
       <c r="Z45" s="3">
         <v>300</v>
       </c>
       <c r="AA45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E46" s="3">
         <v>6900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>26200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>45600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>28200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>800</v>
-      </c>
-      <c r="W46" s="3">
-        <v>1100</v>
       </c>
       <c r="X46" s="3">
         <v>1100</v>
       </c>
       <c r="Y46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z46" s="3">
         <v>3700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3767,93 +3872,96 @@
         <v>0</v>
       </c>
       <c r="Z47" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="3">
         <v>1100</v>
       </c>
       <c r="AB47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC47" s="3">
         <v>1700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>5200</v>
       </c>
       <c r="R48" s="3">
         <v>5200</v>
       </c>
       <c r="S48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="T48" s="3">
         <v>5500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>500</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>200</v>
       </c>
       <c r="AA48" s="3">
         <v>200</v>
@@ -3862,13 +3970,16 @@
         <v>200</v>
       </c>
       <c r="AC48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD48" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3879,7 +3990,7 @@
         <v>200</v>
       </c>
       <c r="F49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G49" s="3">
         <v>300</v>
@@ -3894,49 +4005,49 @@
         <v>300</v>
       </c>
       <c r="K49" s="3">
+        <v>300</v>
+      </c>
+      <c r="L49" s="3">
         <v>3700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>10800</v>
       </c>
       <c r="N49" s="3">
         <v>10800</v>
       </c>
       <c r="O49" s="3">
+        <v>10800</v>
+      </c>
+      <c r="P49" s="3">
         <v>3200</v>
-      </c>
-      <c r="P49" s="3">
-        <v>6100</v>
       </c>
       <c r="Q49" s="3">
         <v>6100</v>
       </c>
       <c r="R49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="S49" s="3">
         <v>6200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19200</v>
-      </c>
-      <c r="U49" s="3">
-        <v>19300</v>
       </c>
       <c r="V49" s="3">
         <v>19300</v>
       </c>
       <c r="W49" s="3">
+        <v>19300</v>
+      </c>
+      <c r="X49" s="3">
         <v>28300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>28400</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>1000</v>
       </c>
       <c r="Z49" s="3">
         <v>1000</v>
@@ -3945,7 +4056,7 @@
         <v>1000</v>
       </c>
       <c r="AB49" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AC49" s="3">
         <v>100</v>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,8 +4242,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4143,13 +4263,13 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -4161,13 +4281,13 @@
         <v>100</v>
       </c>
       <c r="N52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -4175,8 +4295,8 @@
       <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
+      <c r="S52" s="3">
+        <v>100</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
@@ -4193,8 +4313,8 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4420,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10600</v>
+        <v>7500</v>
       </c>
       <c r="E54" s="3">
         <v>10600</v>
       </c>
       <c r="F54" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G54" s="3">
         <v>14400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>51200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>56900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>27500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>25000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,76 +4577,77 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>900</v>
       </c>
       <c r="K57" s="3">
         <v>900</v>
       </c>
       <c r="L57" s="3">
+        <v>900</v>
+      </c>
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1000</v>
       </c>
       <c r="O57" s="3">
         <v>1000</v>
       </c>
       <c r="P57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3500</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>400</v>
       </c>
       <c r="Z57" s="3">
         <v>400</v>
@@ -4525,39 +4656,42 @@
         <v>400</v>
       </c>
       <c r="AB57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
       </c>
       <c r="AD57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>300</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+        <v>700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>400</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -4568,8 +4702,8 @@
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4581,241 +4715,250 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>4400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>2700</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>700</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="U59" s="3">
+        <v>7800</v>
+      </c>
+      <c r="V59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="W59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="X59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="Y59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="O59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="P59" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="R59" s="3">
-        <v>3500</v>
-      </c>
-      <c r="S59" s="3">
-        <v>4200</v>
-      </c>
-      <c r="T59" s="3">
-        <v>7800</v>
-      </c>
-      <c r="U59" s="3">
-        <v>5400</v>
-      </c>
-      <c r="V59" s="3">
-        <v>2900</v>
-      </c>
-      <c r="W59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="X59" s="3">
-        <v>2100</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3800</v>
-      </c>
-      <c r="I60" s="3">
-        <v>3900</v>
       </c>
       <c r="J60" s="3">
         <v>3900</v>
       </c>
       <c r="K60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="L60" s="3">
         <v>3500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4848,11 +4991,11 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>2100</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4877,31 +5020,34 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2000</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
@@ -4910,47 +5056,47 @@
         <v>100</v>
       </c>
       <c r="M62" s="3">
+        <v>100</v>
+      </c>
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>300</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4960,11 +5106,14 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5376,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6500</v>
+        <v>5500</v>
       </c>
       <c r="E66" s="3">
         <v>6500</v>
       </c>
       <c r="F66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G66" s="3">
         <v>6100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5854,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-178300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-175200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-172000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-167800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-164300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-161100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-157200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-153800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-145900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-141800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-131400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-128000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-120300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-114800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-112300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-108400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-96900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-90600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-87000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-82500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-68900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-64900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-66400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-63100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-61400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-56500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-54800</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6210,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4100</v>
+        <v>2000</v>
       </c>
       <c r="E76" s="3">
         <v>4100</v>
       </c>
       <c r="F76" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G76" s="3">
         <v>8300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>33500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>35500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22300</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>100</v>
       </c>
       <c r="Z76" s="3">
         <v>100</v>
       </c>
       <c r="AA76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB76" s="3">
         <v>3000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,13 +6606,14 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>200</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -6432,7 +6631,7 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -6444,10 +6643,10 @@
         <v>300</v>
       </c>
       <c r="N83" s="3">
+        <v>300</v>
+      </c>
+      <c r="O83" s="3">
         <v>400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
@@ -6462,7 +6661,7 @@
         <v>300</v>
       </c>
       <c r="T83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
@@ -6477,25 +6676,28 @@
         <v>200</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
       <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
         <v>100</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
-      </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3400</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-3100</v>
       </c>
       <c r="G89" s="3">
         <v>-3100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1900</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-2000</v>
       </c>
       <c r="Y89" s="3">
         <v>-2000</v>
       </c>
       <c r="Z89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,13 +7262,14 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7059,53 +7280,53 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
@@ -7113,23 +7334,26 @@
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,13 +7527,16 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7317,48 +7547,48 @@
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
       </c>
       <c r="L94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9800</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-200</v>
       </c>
       <c r="P94" s="3">
         <v>-200</v>
       </c>
       <c r="Q94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R94" s="3">
         <v>-400</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-100</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -7369,25 +7599,28 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-100</v>
       </c>
       <c r="AB94" s="3">
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD94" s="3">
         <v>100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,117 +8005,123 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-100</v>
       </c>
       <c r="F100" s="3">
         <v>-100</v>
       </c>
       <c r="G100" s="3">
-        <v>300</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>6700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>20000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>30300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2200</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>300</v>
       </c>
       <c r="AB100" s="3">
         <v>300</v>
       </c>
       <c r="AC100" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD100" s="3">
         <v>3000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7934,90 +8183,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3200</v>
       </c>
-      <c r="G102" s="3">
-        <v>-2800</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1000</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
   <si>
     <t>POAI</t>
   </si>
@@ -656,208 +656,215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>600</v>
+      </c>
+      <c r="F8" s="3">
         <v>300</v>
-      </c>
-      <c r="E8" s="3">
-        <v>300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>400</v>
       </c>
       <c r="G8" s="3">
         <v>300</v>
       </c>
       <c r="H8" s="3">
+        <v>400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>300</v>
+      </c>
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>500</v>
       </c>
       <c r="M8" s="3">
         <v>400</v>
       </c>
       <c r="N8" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="O8" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P8" s="3">
         <v>300</v>
       </c>
       <c r="Q8" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R8" s="3">
         <v>300</v>
       </c>
       <c r="S8" s="3">
+        <v>400</v>
+      </c>
+      <c r="T8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
+        <v>300</v>
+      </c>
+      <c r="V8" s="3">
         <v>500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>300</v>
-      </c>
-      <c r="W8" s="3">
-        <v>300</v>
-      </c>
-      <c r="X8" s="3">
-        <v>500</v>
       </c>
       <c r="Y8" s="3">
         <v>300</v>
       </c>
       <c r="Z8" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AA8" s="3">
         <v>300</v>
@@ -866,24 +873,30 @@
         <v>300</v>
       </c>
       <c r="AC8" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE8" s="3">
         <v>400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F9" s="3">
         <v>200</v>
@@ -892,7 +905,7 @@
         <v>200</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I9" s="3">
         <v>200</v>
@@ -907,7 +920,7 @@
         <v>100</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
@@ -928,25 +941,25 @@
         <v>100</v>
       </c>
       <c r="T9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U9" s="3">
         <v>100</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
       </c>
       <c r="X9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
         <v>100</v>
       </c>
       <c r="Z9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA9" s="3">
         <v>100</v>
@@ -963,8 +976,14 @@
       <c r="AE9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,70 +991,70 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>200</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
       <c r="H10" s="3">
+        <v>200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>300</v>
-      </c>
-      <c r="N10" s="3">
-        <v>200</v>
-      </c>
-      <c r="O10" s="3">
-        <v>400</v>
       </c>
       <c r="P10" s="3">
         <v>200</v>
       </c>
       <c r="Q10" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
       </c>
       <c r="S10" s="3">
+        <v>300</v>
+      </c>
+      <c r="T10" s="3">
         <v>200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
+        <v>200</v>
+      </c>
+      <c r="V10" s="3">
         <v>300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>200</v>
-      </c>
-      <c r="W10" s="3">
-        <v>200</v>
-      </c>
-      <c r="X10" s="3">
-        <v>300</v>
       </c>
       <c r="Y10" s="3">
         <v>200</v>
       </c>
       <c r="Z10" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA10" s="3">
         <v>200</v>
@@ -1044,16 +1063,22 @@
         <v>200</v>
       </c>
       <c r="AC10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE10" s="3">
         <v>300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,29 +1110,31 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,77 +1296,83 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>3500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>7200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>2800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>11600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>3000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>8900</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1346,14 +1385,20 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1361,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
@@ -1373,16 +1418,16 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
+      <c r="K15" s="3">
+        <v>200</v>
+      </c>
+      <c r="L15" s="3">
+        <v>200</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
@@ -1393,11 +1438,11 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1441,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,97 +1522,105 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4700</v>
       </c>
-      <c r="G17" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J17" s="3">
         <v>3400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>10900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>14500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>4000</v>
-      </c>
-      <c r="W17" s="3">
-        <v>12100</v>
       </c>
       <c r="X17" s="3">
         <v>4000</v>
       </c>
       <c r="Y17" s="3">
+        <v>12100</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA17" s="3">
         <v>5400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3100</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>1800</v>
       </c>
       <c r="AD17" s="3">
         <v>2200</v>
       </c>
       <c r="AE17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AG17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1569,88 +1628,94 @@
         <v>-2300</v>
       </c>
       <c r="E18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="L18" s="3">
         <v>-3500</v>
       </c>
-      <c r="H18" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="T18" s="3">
         <v>-3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="U18" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="W18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-3500</v>
       </c>
-      <c r="K18" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1747,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1691,19 +1758,19 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1715,10 +1782,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
@@ -1727,52 +1794,58 @@
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>6600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1780,88 +1853,94 @@
         <v>-2300</v>
       </c>
       <c r="E21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="L21" s="3">
         <v>-3200</v>
       </c>
-      <c r="H21" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="T21" s="3">
         <v>-3600</v>
       </c>
-      <c r="J21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-11200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-6000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-3400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-4300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-13300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1886,11 +1965,11 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1949,8 +2028,14 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1958,88 +2043,94 @@
         <v>-2300</v>
       </c>
       <c r="E23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-4200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-7900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-10400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-8400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-11500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-6300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-4500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-13600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2076,15 +2167,15 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-700</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>8</v>
       </c>
@@ -2094,11 +2185,11 @@
       <c r="T24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2127,8 +2218,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,8 +2313,14 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2225,177 +2328,189 @@
         <v>-2300</v>
       </c>
       <c r="E26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-10400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-7800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-11500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-6300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-4500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-13600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-7900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-10400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-7800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-11500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-6900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-4500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-13700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,32 +2598,38 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="3">
         <v>-800</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J29" s="3">
         <v>-400</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2883,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2759,19 +2898,19 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2783,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
@@ -2795,141 +2934,153 @@
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-7900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-10400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-7800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-11500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-6900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-4500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-13700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-7900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-10400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-7800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-11500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-6900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-4500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-13700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,8 +3437,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3275,88 +3448,94 @@
         <v>3100</v>
       </c>
       <c r="E41" s="3">
+        <v>700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G41" s="3">
         <v>5300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>22100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>25400</v>
-      </c>
-      <c r="M41" s="3">
-        <v>28200</v>
-      </c>
-      <c r="N41" s="3">
-        <v>25100</v>
       </c>
       <c r="O41" s="3">
         <v>28200</v>
       </c>
       <c r="P41" s="3">
+        <v>25100</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>28200</v>
+      </c>
+      <c r="R41" s="3">
         <v>41800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>44900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>27300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3442,36 +3621,42 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="F43" s="3">
         <v>500</v>
       </c>
       <c r="G43" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H43" s="3">
         <v>500</v>
       </c>
       <c r="I43" s="3">
+        <v>300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>500</v>
+      </c>
+      <c r="K43" s="3">
         <v>400</v>
-      </c>
-      <c r="J43" s="3">
-        <v>300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>300</v>
       </c>
       <c r="L43" s="3">
         <v>300</v>
@@ -3483,78 +3668,84 @@
         <v>300</v>
       </c>
       <c r="O43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P43" s="3">
         <v>300</v>
       </c>
       <c r="Q43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="R43" s="3">
         <v>300</v>
       </c>
       <c r="S43" s="3">
+        <v>200</v>
+      </c>
+      <c r="T43" s="3">
         <v>300</v>
-      </c>
-      <c r="T43" s="3">
-        <v>500</v>
       </c>
       <c r="U43" s="3">
         <v>300</v>
       </c>
       <c r="V43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="W43" s="3">
         <v>300</v>
       </c>
       <c r="X43" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z43" s="3">
         <v>600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>400</v>
+      </c>
+      <c r="F44" s="3">
         <v>500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>600</v>
-      </c>
-      <c r="F44" s="3">
-        <v>400</v>
-      </c>
-      <c r="G44" s="3">
-        <v>500</v>
       </c>
       <c r="H44" s="3">
         <v>400</v>
       </c>
       <c r="I44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J44" s="3">
         <v>400</v>
@@ -3563,34 +3754,34 @@
         <v>400</v>
       </c>
       <c r="L44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N44" s="3">
         <v>500</v>
       </c>
       <c r="O44" s="3">
+        <v>500</v>
+      </c>
+      <c r="P44" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q44" s="3">
         <v>400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>400</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>300</v>
-      </c>
-      <c r="R44" s="3">
-        <v>300</v>
       </c>
       <c r="S44" s="3">
         <v>300</v>
       </c>
       <c r="T44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V44" s="3">
         <v>200</v>
@@ -3602,13 +3793,13 @@
         <v>200</v>
       </c>
       <c r="Y44" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA44" s="3">
         <v>300</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>300</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>200</v>
       </c>
       <c r="AB44" s="3">
         <v>300</v>
@@ -3620,21 +3811,27 @@
         <v>300</v>
       </c>
       <c r="AE44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF44" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
+        <v>100</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -3642,166 +3839,178 @@
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
+      <c r="I45" s="3">
+        <v>100</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>300</v>
       </c>
       <c r="T45" s="3">
         <v>300</v>
       </c>
       <c r="U45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V45" s="3">
         <v>300</v>
       </c>
       <c r="W45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Y45" s="3">
         <v>200</v>
       </c>
       <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB45" s="3">
         <v>300</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>300</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>400</v>
       </c>
       <c r="AC45" s="3">
         <v>300</v>
       </c>
       <c r="AD45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AE45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F46" s="3">
         <v>4600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>16000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>19800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>23400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>26900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>29800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>26200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>29500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>43000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>45600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>28200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>3100</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>2000</v>
       </c>
       <c r="AD46" s="3">
         <v>3100</v>
       </c>
       <c r="AE46" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AG46" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3826,11 +4035,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3875,116 +4084,128 @@
         <v>0</v>
       </c>
       <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
         <v>1100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>1700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>2700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F48" s="3">
         <v>2600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3700</v>
       </c>
-      <c r="G48" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J48" s="3">
         <v>4300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>500</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>200</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>200</v>
       </c>
       <c r="AC48" s="3">
         <v>200</v>
       </c>
       <c r="AD48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF48" s="3">
         <v>100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>200</v>
@@ -3993,13 +4214,13 @@
         <v>200</v>
       </c>
       <c r="G49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J49" s="3">
         <v>300</v>
@@ -4008,67 +4229,73 @@
         <v>300</v>
       </c>
       <c r="L49" s="3">
+        <v>300</v>
+      </c>
+      <c r="M49" s="3">
+        <v>300</v>
+      </c>
+      <c r="N49" s="3">
         <v>3700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>10800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>10800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>6100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>6100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>6200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>16200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>19200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>19300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>19300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>28300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>28400</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>1000</v>
       </c>
       <c r="AB49" s="3">
         <v>1000</v>
       </c>
       <c r="AC49" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AD49" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AE49" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,8 +4478,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4266,16 +4505,16 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -4284,25 +4523,25 @@
         <v>100</v>
       </c>
       <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>200</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>100</v>
-      </c>
-      <c r="R52" s="3">
-        <v>100</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
+      <c r="T52" s="3">
+        <v>100</v>
+      </c>
+      <c r="U52" s="3">
+        <v>100</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
@@ -4316,11 +4555,11 @@
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4334,8 +4573,14 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F54" s="3">
         <v>7500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>14400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>18200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>21000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>25100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>25700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>33200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>36500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>40100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>43800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>51200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>56900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>39700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>13100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>25200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>27500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>25000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>22400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>31900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>32300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>5400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>4000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>6000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,138 +4837,146 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1100</v>
       </c>
       <c r="O57" s="3">
         <v>1000</v>
       </c>
       <c r="P57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>900</v>
       </c>
       <c r="R57" s="3">
         <v>1000</v>
       </c>
       <c r="S57" s="3">
+        <v>900</v>
+      </c>
+      <c r="T57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3500</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>400</v>
       </c>
       <c r="AB57" s="3">
         <v>400</v>
       </c>
       <c r="AC57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE57" s="3">
         <v>200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>600</v>
+      </c>
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
-        <v>700</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>600</v>
+      </c>
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4718,46 +4985,52 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>4400</v>
       </c>
       <c r="V58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="W58" s="3">
+        <v>4400</v>
+      </c>
+      <c r="X58" s="3">
         <v>3800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>4800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>4500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4765,207 +5038,219 @@
         <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
         <v>300</v>
       </c>
       <c r="H59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>500</v>
+      </c>
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>7800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F60" s="3">
         <v>3800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
-      </c>
-      <c r="O60" s="3">
-        <v>3200</v>
-      </c>
-      <c r="P60" s="3">
-        <v>3000</v>
       </c>
       <c r="Q60" s="3">
         <v>3200</v>
       </c>
       <c r="R60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S60" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T60" s="3">
         <v>3300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>9300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>11600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>14700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>12400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>10800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>9500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>4800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F61" s="3">
         <v>1700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2000</v>
       </c>
-      <c r="G61" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J61" s="3">
         <v>2300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4994,14 +5279,14 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>2100</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5023,8 +5308,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5034,8 +5325,8 @@
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>8</v>
@@ -5043,77 +5334,83 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
+      <c r="I62" s="3">
+        <v>100</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>100</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
       <c r="N62" s="3">
+        <v>100</v>
+      </c>
+      <c r="O62" s="3">
+        <v>100</v>
+      </c>
+      <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>300</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F66" s="3">
         <v>5500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6500</v>
-      </c>
-      <c r="F66" s="3">
-        <v>6500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>6100</v>
       </c>
       <c r="H66" s="3">
         <v>6500</v>
       </c>
       <c r="I66" s="3">
-        <v>6300</v>
+        <v>6100</v>
       </c>
       <c r="J66" s="3">
         <v>6500</v>
       </c>
       <c r="K66" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="M66" s="3">
         <v>4000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>10400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>12900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>15800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>14700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>11100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>11200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>10000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-182900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-180400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-178300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-175200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-172000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-167800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-164300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-161100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-157200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-153800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-145900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-141800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-131400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-128000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-114800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-112300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-108400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-96900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-90600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-87000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-82500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-68900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-64900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-66400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-63100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-61400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-56500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-54800</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F76" s="3">
         <v>2000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>18600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>21800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>29600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>33500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>37200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>40300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>47800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>53100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>35500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>12200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>11700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>10300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>11200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>20700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>22300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>3000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>3400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-7900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-10400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-7800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-11500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-6900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-4500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-13700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,19 +7002,21 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
+        <v>500</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -6634,10 +7031,10 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
@@ -6646,13 +7043,13 @@
         <v>300</v>
       </c>
       <c r="O83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
@@ -6664,10 +7061,10 @@
         <v>300</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -6679,25 +7076,31 @@
         <v>200</v>
       </c>
       <c r="Z83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>-800</v>
       </c>
       <c r="E89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>-3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-3300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-3200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-3700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-3000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7702,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7274,29 +7715,29 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -7311,49 +7752,55 @@
         <v>-200</v>
       </c>
       <c r="R91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
+      <c r="T91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-200</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,71 +7983,77 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>600</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-200</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-9800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -7602,25 +8061,31 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7678,11 +8145,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,97 +8493,109 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>2500</v>
       </c>
       <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>3400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>6700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>20000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>30300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>4000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>5900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>3600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>2200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>3000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8123,11 +8620,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8186,93 +8683,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="E102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3200</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3100</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-13600</v>
       </c>
       <c r="P102" s="3">
         <v>-3100</v>
       </c>
       <c r="Q102" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="R102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="S102" s="3">
         <v>17600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>26600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1000</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/POAI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>POAI</t>
   </si>
@@ -656,218 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>600</v>
-      </c>
-      <c r="F8" s="3">
-        <v>300</v>
       </c>
       <c r="G8" s="3">
         <v>300</v>
       </c>
       <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>300</v>
+      </c>
+      <c r="K8" s="3">
+        <v>700</v>
+      </c>
+      <c r="L8" s="3">
+        <v>500</v>
+      </c>
+      <c r="M8" s="3">
+        <v>200</v>
+      </c>
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="O8" s="3">
+        <v>500</v>
+      </c>
+      <c r="P8" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
-        <v>700</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="R8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
-        <v>200</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="S8" s="3">
+        <v>300</v>
+      </c>
+      <c r="T8" s="3">
         <v>400</v>
-      </c>
-      <c r="N8" s="3">
-        <v>500</v>
-      </c>
-      <c r="O8" s="3">
-        <v>400</v>
-      </c>
-      <c r="P8" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>500</v>
-      </c>
-      <c r="R8" s="3">
-        <v>300</v>
-      </c>
-      <c r="S8" s="3">
-        <v>400</v>
-      </c>
-      <c r="T8" s="3">
-        <v>300</v>
       </c>
       <c r="U8" s="3">
         <v>300</v>
       </c>
       <c r="V8" s="3">
+        <v>300</v>
+      </c>
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>200</v>
-      </c>
-      <c r="X8" s="3">
-        <v>300</v>
       </c>
       <c r="Y8" s="3">
         <v>300</v>
       </c>
       <c r="Z8" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA8" s="3">
         <v>500</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>300</v>
       </c>
       <c r="AB8" s="3">
         <v>300</v>
@@ -879,16 +883,19 @@
         <v>300</v>
       </c>
       <c r="AE8" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AF8" s="3">
         <v>400</v>
       </c>
       <c r="AG8" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -896,34 +903,34 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>300</v>
-      </c>
-      <c r="F9" s="3">
-        <v>200</v>
       </c>
       <c r="G9" s="3">
         <v>200</v>
       </c>
       <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>100</v>
-      </c>
-      <c r="M9" s="3">
-        <v>200</v>
-      </c>
-      <c r="N9" s="3">
-        <v>100</v>
       </c>
       <c r="O9" s="3">
         <v>100</v>
@@ -947,10 +954,10 @@
         <v>100</v>
       </c>
       <c r="V9" s="3">
+        <v>100</v>
+      </c>
+      <c r="W9" s="3">
         <v>200</v>
-      </c>
-      <c r="W9" s="3">
-        <v>100</v>
       </c>
       <c r="X9" s="3">
         <v>100</v>
@@ -959,10 +966,10 @@
         <v>100</v>
       </c>
       <c r="Z9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA9" s="3">
         <v>200</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>100</v>
       </c>
       <c r="AB9" s="3">
         <v>100</v>
@@ -982,82 +989,85 @@
       <c r="AG9" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>300</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
       <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>600</v>
+      </c>
+      <c r="L10" s="3">
+        <v>300</v>
+      </c>
+      <c r="M10" s="3">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
-        <v>100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>600</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
+        <v>400</v>
+      </c>
+      <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
+        <v>200</v>
+      </c>
+      <c r="T10" s="3">
         <v>300</v>
-      </c>
-      <c r="P10" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>400</v>
-      </c>
-      <c r="R10" s="3">
-        <v>200</v>
-      </c>
-      <c r="S10" s="3">
-        <v>300</v>
-      </c>
-      <c r="T10" s="3">
-        <v>200</v>
       </c>
       <c r="U10" s="3">
         <v>200</v>
       </c>
       <c r="V10" s="3">
+        <v>200</v>
+      </c>
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>100</v>
-      </c>
-      <c r="X10" s="3">
-        <v>200</v>
       </c>
       <c r="Y10" s="3">
         <v>200</v>
       </c>
       <c r="Z10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA10" s="3">
         <v>300</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>200</v>
       </c>
       <c r="AB10" s="3">
         <v>200</v>
@@ -1069,16 +1079,19 @@
         <v>200</v>
       </c>
       <c r="AE10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF10" s="3">
         <v>300</v>
       </c>
       <c r="AG10" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH10" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,19 +1125,20 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1132,12 +1146,12 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,19 +1319,22 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1322,60 +1342,60 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>3500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>7200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>4100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2800</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>11600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8900</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1391,14 +1411,17 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1412,16 +1435,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
@@ -1429,8 +1452,8 @@
       <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
+      <c r="M15" s="3">
+        <v>200</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
@@ -1444,8 +1467,8 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2700</v>
       </c>
       <c r="F17" s="3">
         <v>2700</v>
       </c>
       <c r="G17" s="3">
-        <v>3500</v>
+        <v>2700</v>
       </c>
       <c r="H17" s="3">
-        <v>4700</v>
+        <v>2500</v>
       </c>
       <c r="I17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6100</v>
-      </c>
-      <c r="W17" s="3">
-        <v>4000</v>
       </c>
       <c r="X17" s="3">
         <v>4000</v>
       </c>
       <c r="Y17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z17" s="3">
         <v>12100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H18" s="3">
-        <v>-4200</v>
+        <v>-2500</v>
       </c>
       <c r="I18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-3000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-14200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,20 +1782,21 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1770,11 +1804,11 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1788,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
@@ -1800,147 +1834,153 @@
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-600</v>
       </c>
       <c r="AD20" s="3">
         <v>-600</v>
       </c>
       <c r="AE20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-3000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="R21" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="U21" s="3">
         <v>-3600</v>
       </c>
-      <c r="L21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-11200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-2400</v>
       </c>
       <c r="AE21" s="3">
         <v>-2400</v>
       </c>
       <c r="AF21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1971,8 +2011,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2034,103 +2074,109 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H23" s="3">
-        <v>-4200</v>
+        <v>-2500</v>
       </c>
       <c r="I23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2173,12 +2219,12 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>8</v>
       </c>
@@ -2191,8 +2237,8 @@
       <c r="V24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -2224,8 +2270,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H26" s="3">
-        <v>-4200</v>
+        <v>-2500</v>
       </c>
       <c r="I26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J26" s="3">
         <v>-3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,35 +2662,38 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E29" s="3">
         <v>-200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-800</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="I29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J29" s="3">
         <v>-500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-400</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,20 +2956,23 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2910,11 +2980,11 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2928,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
@@ -2940,147 +3010,153 @@
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>600</v>
       </c>
       <c r="AD32" s="3">
         <v>600</v>
       </c>
       <c r="AE32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3525,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>3100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>200</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>100</v>
       </c>
       <c r="AA41" s="3">
         <v>100</v>
       </c>
       <c r="AB41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC41" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>200</v>
       </c>
       <c r="AD41" s="3">
         <v>200</v>
       </c>
       <c r="AE41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF41" s="3">
         <v>1000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3627,39 +3717,42 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
-      </c>
-      <c r="L43" s="3">
-        <v>300</v>
       </c>
       <c r="M43" s="3">
         <v>300</v>
@@ -3674,25 +3767,25 @@
         <v>300</v>
       </c>
       <c r="Q43" s="3">
+        <v>300</v>
+      </c>
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
-      </c>
-      <c r="T43" s="3">
-        <v>300</v>
       </c>
       <c r="U43" s="3">
         <v>300</v>
       </c>
       <c r="V43" s="3">
+        <v>300</v>
+      </c>
+      <c r="W43" s="3">
         <v>500</v>
-      </c>
-      <c r="W43" s="3">
-        <v>300</v>
       </c>
       <c r="X43" s="3">
         <v>300</v>
@@ -3701,31 +3794,34 @@
         <v>300</v>
       </c>
       <c r="Z43" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA43" s="3">
         <v>600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3733,22 +3829,22 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>500</v>
-      </c>
-      <c r="J44" s="3">
-        <v>400</v>
       </c>
       <c r="K44" s="3">
         <v>400</v>
@@ -3760,7 +3856,7 @@
         <v>400</v>
       </c>
       <c r="N44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O44" s="3">
         <v>500</v>
@@ -3769,13 +3865,13 @@
         <v>500</v>
       </c>
       <c r="Q44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R44" s="3">
         <v>400</v>
       </c>
       <c r="S44" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T44" s="3">
         <v>300</v>
@@ -3784,7 +3880,7 @@
         <v>300</v>
       </c>
       <c r="V44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W44" s="3">
         <v>200</v>
@@ -3799,33 +3895,36 @@
         <v>200</v>
       </c>
       <c r="AA44" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB44" s="3">
         <v>300</v>
       </c>
       <c r="AC44" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD44" s="3">
         <v>200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>200</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>300</v>
       </c>
       <c r="AG44" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -3833,47 +3932,47 @@
       <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
+      <c r="G45" s="3">
+        <v>100</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>300</v>
       </c>
       <c r="U45" s="3">
         <v>300</v>
@@ -3882,135 +3981,141 @@
         <v>300</v>
       </c>
       <c r="W45" s="3">
+        <v>300</v>
+      </c>
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>300</v>
       </c>
       <c r="AC45" s="3">
         <v>300</v>
       </c>
       <c r="AD45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>26900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>26200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>43000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>45600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>28200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>800</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>1100</v>
       </c>
       <c r="AA46" s="3">
         <v>1100</v>
       </c>
       <c r="AB46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC46" s="3">
         <v>3700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4041,8 +4146,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4090,102 +4195,105 @@
         <v>0</v>
       </c>
       <c r="AC47" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="AD47" s="3">
         <v>1100</v>
       </c>
       <c r="AE47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF47" s="3">
         <v>1700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5100</v>
-      </c>
-      <c r="T48" s="3">
-        <v>5200</v>
       </c>
       <c r="U48" s="3">
         <v>5200</v>
       </c>
       <c r="V48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="W48" s="3">
         <v>5500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>500</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>200</v>
       </c>
       <c r="AD48" s="3">
         <v>200</v>
@@ -4194,13 +4302,16 @@
         <v>200</v>
       </c>
       <c r="AF48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG48" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4208,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>200</v>
@@ -4223,7 +4334,7 @@
         <v>200</v>
       </c>
       <c r="J49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K49" s="3">
         <v>300</v>
@@ -4235,49 +4346,49 @@
         <v>300</v>
       </c>
       <c r="N49" s="3">
+        <v>300</v>
+      </c>
+      <c r="O49" s="3">
         <v>3700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>10800</v>
       </c>
       <c r="Q49" s="3">
         <v>10800</v>
       </c>
       <c r="R49" s="3">
+        <v>10800</v>
+      </c>
+      <c r="S49" s="3">
         <v>3200</v>
-      </c>
-      <c r="S49" s="3">
-        <v>6100</v>
       </c>
       <c r="T49" s="3">
         <v>6100</v>
       </c>
       <c r="U49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="V49" s="3">
         <v>6200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>19200</v>
-      </c>
-      <c r="X49" s="3">
-        <v>19300</v>
       </c>
       <c r="Y49" s="3">
         <v>19300</v>
       </c>
       <c r="Z49" s="3">
+        <v>19300</v>
+      </c>
+      <c r="AA49" s="3">
         <v>28300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>28400</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>1000</v>
       </c>
       <c r="AC49" s="3">
         <v>1000</v>
@@ -4286,7 +4397,7 @@
         <v>1000</v>
       </c>
       <c r="AE49" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF49" s="3">
         <v>100</v>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4601,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4505,19 +4625,19 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>200</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -4529,13 +4649,13 @@
         <v>100</v>
       </c>
       <c r="Q52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -4543,8 +4663,8 @@
       <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>8</v>
+      <c r="V52" s="3">
+        <v>100</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>8</v>
@@ -4561,8 +4681,8 @@
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>10600</v>
       </c>
       <c r="H54" s="3">
         <v>10600</v>
       </c>
       <c r="I54" s="3">
+        <v>10600</v>
+      </c>
+      <c r="J54" s="3">
         <v>14400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>43800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>51200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>56900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>39700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>25200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>25000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>31900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>32300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,85 +4969,86 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1100</v>
       </c>
       <c r="F57" s="3">
         <v>1100</v>
       </c>
       <c r="G57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>900</v>
       </c>
       <c r="N57" s="3">
         <v>900</v>
       </c>
       <c r="O57" s="3">
+        <v>900</v>
+      </c>
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1000</v>
       </c>
       <c r="R57" s="3">
         <v>1000</v>
       </c>
       <c r="S57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3500</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>400</v>
       </c>
       <c r="AC57" s="3">
         <v>400</v>
@@ -4926,49 +5057,52 @@
         <v>400</v>
       </c>
       <c r="AE57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AF57" s="3">
         <v>200</v>
       </c>
       <c r="AG57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>600</v>
       </c>
       <c r="I58" s="3">
         <v>600</v>
       </c>
       <c r="J58" s="3">
+        <v>600</v>
+      </c>
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4978,8 +5112,8 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4991,46 +5125,49 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>4400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5044,216 +5181,222 @@
         <v>500</v>
       </c>
       <c r="G59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H59" s="3">
         <v>300</v>
       </c>
       <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3800</v>
-      </c>
-      <c r="L60" s="3">
-        <v>3900</v>
       </c>
       <c r="M60" s="3">
         <v>3900</v>
       </c>
       <c r="N60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O60" s="3">
         <v>3500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5285,11 +5428,11 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>2100</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5314,8 +5457,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5334,20 +5480,20 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>100</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -5356,47 +5502,47 @@
         <v>100</v>
       </c>
       <c r="P62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>300</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5406,11 +5552,14 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E66" s="3">
         <v>6000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>6500</v>
       </c>
       <c r="H66" s="3">
         <v>6500</v>
       </c>
       <c r="I66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J66" s="3">
         <v>6100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-184900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-182900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-180400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-178300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-175200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-172000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-167800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-164300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-161100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-157200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-153800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-145900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-141800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-131400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-128000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-120300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-114800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-112300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-108400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-96900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-90600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-87000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-82500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-68900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-64900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-66400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-63100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-61400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-56500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-54800</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2000</v>
-      </c>
-      <c r="G76" s="3">
-        <v>4100</v>
       </c>
       <c r="H76" s="3">
         <v>4100</v>
       </c>
       <c r="I76" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J76" s="3">
         <v>8300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>29600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>33500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>40300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>53100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>35500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22300</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>100</v>
       </c>
       <c r="AC76" s="3">
         <v>100</v>
       </c>
       <c r="AD76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE76" s="3">
         <v>3000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7013,13 +7212,13 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>500</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -7037,7 +7236,7 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
@@ -7049,10 +7248,10 @@
         <v>300</v>
       </c>
       <c r="Q83" s="3">
+        <v>300</v>
+      </c>
+      <c r="R83" s="3">
         <v>400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
@@ -7067,7 +7266,7 @@
         <v>300</v>
       </c>
       <c r="W83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -7082,25 +7281,28 @@
         <v>200</v>
       </c>
       <c r="AB83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
       <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
         <v>100</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>-3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3100</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>-3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-2000</v>
       </c>
       <c r="AB89" s="3">
         <v>-2000</v>
       </c>
       <c r="AC89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,22 +7924,23 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -7727,56 +7948,56 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
@@ -7784,23 +8005,26 @@
       <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,22 +8216,25 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -8012,51 +8242,51 @@
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9800</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-200</v>
       </c>
       <c r="S94" s="3">
         <v>-200</v>
       </c>
       <c r="T94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U94" s="3">
         <v>-400</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
       <c r="W94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -8067,25 +8297,28 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-100</v>
       </c>
       <c r="AE94" s="3">
         <v>-100</v>
       </c>
       <c r="AF94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG94" s="3">
         <v>100</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8151,8 +8385,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,31 +8742,34 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>3400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
+      <c r="J100" s="3">
+        <v>-100</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -8531,71 +8777,74 @@
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>6700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>20000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>30300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2200</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>300</v>
       </c>
       <c r="AE100" s="3">
         <v>300</v>
       </c>
       <c r="AF100" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG100" s="3">
         <v>3000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8626,8 +8875,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8689,99 +8938,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2300</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3200</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>17600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>26600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1000</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>
